--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484611_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484611_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. GARCIA ROYO</t>
+          <t>P. MORTE MONTANES</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8844</v>
+        <v>5.4926</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5184</v>
+        <v>2.2398</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3659</v>
+        <v>3.2528</v>
       </c>
       <c r="G2" t="n">
-        <v>4.5146</v>
+        <v>5.0133</v>
       </c>
       <c r="H2" t="n">
-        <v>4.5082</v>
+        <v>2.5447</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0064</v>
+        <v>2.4686</v>
       </c>
       <c r="J2" t="n">
-        <v>5.095</v>
+        <v>4.3359</v>
       </c>
       <c r="K2" t="n">
-        <v>4.9601</v>
+        <v>2.3159</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1349</v>
+        <v>2.0201</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.5804</v>
+        <v>0.6774</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4519</v>
+        <v>0.2288</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1285</v>
+        <v>0.4486</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.733</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q2" t="n">
         <v>-3.6651</v>
       </c>
       <c r="R2" t="n">
-        <v>2.9321</v>
+        <v>2.7489</v>
       </c>
       <c r="S2" t="n">
-        <v>3.6605</v>
+        <v>1.7176</v>
       </c>
       <c r="T2" t="n">
-        <v>2.6908</v>
+        <v>1.569</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9697</v>
+        <v>0.1485</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.5577</v>
+        <v>-0.3219</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.6022999999999999</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.9554</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.5329</v>
+        <v>5.3541</v>
       </c>
       <c r="E3" t="n">
-        <v>0.964</v>
+        <v>1.033</v>
       </c>
       <c r="F3" t="n">
-        <v>4.5689</v>
+        <v>4.3211</v>
       </c>
       <c r="G3" t="n">
         <v>4.8648</v>
@@ -688,13 +688,13 @@
         <v>3.1154</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1629</v>
+        <v>1.9842</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0966</v>
+        <v>1.1656</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0663</v>
+        <v>0.8186</v>
       </c>
       <c r="V3" t="n">
         <v>-0.945</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. MORAGAS AZNAR</t>
+          <t>D. GARCIA ROYO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.7581</v>
+        <v>4.8348</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.1529</v>
+        <v>2.667</v>
       </c>
       <c r="F4" t="n">
-        <v>6.911</v>
+        <v>2.1678</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8916</v>
+        <v>4.5146</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8371</v>
+        <v>4.5082</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9455</v>
+        <v>0.0064</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.582</v>
+        <v>5.095</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4148</v>
+        <v>4.9601</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.9968</v>
+        <v>0.1349</v>
       </c>
       <c r="M4" t="n">
-        <v>3.4736</v>
+        <v>-0.5804</v>
       </c>
       <c r="N4" t="n">
-        <v>1.4223</v>
+        <v>-0.4519</v>
       </c>
       <c r="O4" t="n">
-        <v>2.0513</v>
+        <v>-0.1285</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8326</v>
+        <v>-0.733</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9163</v>
+        <v>-3.6651</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7489</v>
+        <v>2.9321</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3559</v>
+        <v>2.6109</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3454</v>
+        <v>1.8394</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0104</v>
+        <v>0.7715</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3219</v>
+        <v>-1.5577</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3219</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. MORTE MONTANES</t>
+          <t>M. MORAGAS AZNAR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.5663</v>
+        <v>4.6449</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5117</v>
+        <v>-1.7954</v>
       </c>
       <c r="F5" t="n">
-        <v>3.0546</v>
+        <v>6.4403</v>
       </c>
       <c r="G5" t="n">
-        <v>5.0133</v>
+        <v>1.8916</v>
       </c>
       <c r="H5" t="n">
-        <v>2.5447</v>
+        <v>2.8371</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4686</v>
+        <v>-0.9455</v>
       </c>
       <c r="J5" t="n">
-        <v>4.3359</v>
+        <v>-1.582</v>
       </c>
       <c r="K5" t="n">
-        <v>2.3159</v>
+        <v>1.4148</v>
       </c>
       <c r="L5" t="n">
-        <v>2.0201</v>
+        <v>-2.9968</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6774</v>
+        <v>3.4736</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2288</v>
+        <v>1.4223</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4486</v>
+        <v>2.0513</v>
       </c>
       <c r="P5" t="n">
+        <v>1.8326</v>
+      </c>
+      <c r="Q5" t="n">
         <v>-0.9163</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-3.6651</v>
       </c>
       <c r="R5" t="n">
         <v>2.7489</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7913</v>
+        <v>1.2426</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8409</v>
+        <v>0.7029</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0496</v>
+        <v>0.5397</v>
       </c>
       <c r="V5" t="n">
         <v>-0.3219</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. IGBINS DAVID</t>
+          <t>A. CEJUDO GALAN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.332</v>
+        <v>3.2712</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.221</v>
+        <v>-1.3719</v>
       </c>
       <c r="F6" t="n">
-        <v>2.553</v>
+        <v>4.6431</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.6257</v>
+        <v>1.4344</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8338</v>
+        <v>0.4985</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7917999999999999</v>
+        <v>0.9359</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.8846</v>
+        <v>-0.165</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.4777</v>
+        <v>0.3094</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.4069</v>
+        <v>-0.4743</v>
       </c>
       <c r="M6" t="n">
-        <v>0.259</v>
+        <v>1.5994</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6439</v>
+        <v>0.1891</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3849</v>
+        <v>1.4103</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8326</v>
+        <v>2.5656</v>
       </c>
       <c r="S6" t="n">
-        <v>4.2692</v>
+        <v>1.1037</v>
       </c>
       <c r="T6" t="n">
-        <v>3.8077</v>
+        <v>0.6256</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4615</v>
+        <v>0.4781</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3115</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3115</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. CEJUDO GALAN</t>
+          <t>M. GARRIDO TALENS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.2289</v>
+        <v>2.5339</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.0179</v>
+        <v>2.9167</v>
       </c>
       <c r="F7" t="n">
-        <v>4.2467</v>
+        <v>-0.3828</v>
       </c>
       <c r="G7" t="n">
-        <v>1.4344</v>
+        <v>3.0025</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4985</v>
+        <v>3.509</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9359</v>
+        <v>-0.5065</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.165</v>
+        <v>3.7203</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3094</v>
+        <v>3.5855</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.4743</v>
+        <v>0.1349</v>
       </c>
       <c r="M7" t="n">
-        <v>1.5994</v>
+        <v>-0.7178</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1891</v>
+        <v>-0.0765</v>
       </c>
       <c r="O7" t="n">
-        <v>1.4103</v>
+        <v>-0.6413</v>
       </c>
       <c r="P7" t="n">
-        <v>0.733</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5656</v>
+        <v>1.2828</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0614</v>
+        <v>1.0262</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0203</v>
+        <v>1.3405</v>
       </c>
       <c r="U7" t="n">
-        <v>0.08169999999999999</v>
+        <v>-0.3143</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.945</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.3115</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. CEJUDO GALÁN</t>
+          <t>M. MARIA VENTURA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.9256</v>
+        <v>2.3492</v>
       </c>
       <c r="E8" t="n">
-        <v>1.9256</v>
+        <v>0.7547</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1.5945</v>
       </c>
       <c r="G8" t="n">
-        <v>1.9256</v>
+        <v>0.0029</v>
       </c>
       <c r="H8" t="n">
-        <v>1.3005</v>
+        <v>3.0317</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6251</v>
+        <v>-3.0289</v>
       </c>
       <c r="J8" t="n">
-        <v>1.9256</v>
+        <v>-0.3935</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3005</v>
+        <v>1.994</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6251</v>
+        <v>-2.3876</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>0.3964</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.0377</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-0.6413</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.4661</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.4661</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>0.8803</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.1482</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>-0.2679</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. GARRIDO TALENS</t>
+          <t>A. CEJUDO GALÁN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.7807</v>
+        <v>1.9256</v>
       </c>
       <c r="E9" t="n">
-        <v>2.436</v>
+        <v>1.9256</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6553</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>3.0025</v>
+        <v>1.9256</v>
       </c>
       <c r="H9" t="n">
-        <v>3.509</v>
+        <v>1.3005</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5065</v>
+        <v>0.6251</v>
       </c>
       <c r="J9" t="n">
-        <v>3.7203</v>
+        <v>1.9256</v>
       </c>
       <c r="K9" t="n">
-        <v>3.5855</v>
+        <v>1.3005</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1349</v>
+        <v>0.6251</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7178</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0765</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6413</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.5498</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2828</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2729</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8597</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5868</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.945</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3115</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6335</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. MARIA VENTURA</t>
+          <t>A. IGBINS DAVID</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7279</v>
+        <v>0.6009</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7427</v>
+        <v>-1.7044</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4706</v>
+        <v>2.3053</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0029</v>
+        <v>-1.6257</v>
       </c>
       <c r="H10" t="n">
-        <v>3.0317</v>
+        <v>-0.8338</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.0289</v>
+        <v>-0.7917999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3935</v>
+        <v>-1.8846</v>
       </c>
       <c r="K10" t="n">
-        <v>1.994</v>
+        <v>-1.4777</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.3876</v>
+        <v>-0.4069</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3964</v>
+        <v>0.259</v>
       </c>
       <c r="N10" t="n">
-        <v>1.0377</v>
+        <v>0.6439</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6413</v>
+        <v>-0.3849</v>
       </c>
       <c r="P10" t="n">
-        <v>1.4661</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4661</v>
+        <v>1.8326</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.741</v>
+        <v>2.5381</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3492</v>
+        <v>2.3243</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3918</v>
+        <v>0.2138</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.3115</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.3115</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5553</v>
+        <v>0.1107</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0762</v>
+        <v>-0.5417999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4791</v>
+        <v>0.6525</v>
       </c>
       <c r="G11" t="n">
         <v>-0.7683</v>
@@ -1312,13 +1312,13 @@
         <v>0.5498</v>
       </c>
       <c r="S11" t="n">
-        <v>1.0855</v>
+        <v>0.6408</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9698</v>
+        <v>0.3518</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1156</v>
+        <v>0.289</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3115</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>30.2921</v>
+        <v>31.1179</v>
       </c>
       <c r="E12" t="n">
-        <v>5.297400000000001</v>
+        <v>6.123299999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>24.9945</v>
+        <v>24.9946</v>
       </c>
       <c r="G12" t="n">
         <v>20.2557</v>
@@ -1372,7 +1372,7 @@
         <v>-1.279</v>
       </c>
       <c r="M12" t="n">
-        <v>6.5755</v>
+        <v>6.575500000000001</v>
       </c>
       <c r="N12" t="n">
         <v>2.7307</v>
@@ -1390,16 +1390,16 @@
         <v>19.2422</v>
       </c>
       <c r="S12" t="n">
-        <v>12.9186</v>
+        <v>13.7444</v>
       </c>
       <c r="T12" t="n">
-        <v>10.2414</v>
+        <v>11.0673</v>
       </c>
       <c r="U12" t="n">
         <v>2.677</v>
       </c>
       <c r="V12" t="n">
-        <v>-4.7145</v>
+        <v>-4.714499999999999</v>
       </c>
       <c r="W12" t="n">
         <v>-1.2149</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2907</v>
+        <v>0.1362</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1756</v>
+        <v>0.2717</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4663</v>
+        <v>-0.1356</v>
       </c>
       <c r="G15" t="n">
         <v>0.2645</v>
@@ -1624,13 +1624,13 @@
         <v>0.1833</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7385</v>
+        <v>-0.3116</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2021</v>
+        <v>-0.106</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5364</v>
+        <v>-0.2057</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.6948</v>
+        <v>-0.3539</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1277</v>
+        <v>0.32</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8225</v>
+        <v>-0.6738</v>
       </c>
       <c r="G16" t="n">
         <v>-0.72</v>
@@ -1702,13 +1702,13 @@
         <v>0.9163</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8911</v>
+        <v>-0.5501</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3492</v>
+        <v>-0.1568</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5419</v>
+        <v>-0.3933</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7836</v>
+        <v>-0.5913</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4689</v>
+        <v>0.6612</v>
       </c>
       <c r="F17" t="n">
         <v>-1.2525</v>
@@ -1780,10 +1780,10 @@
         <v>0.5498</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2089</v>
+        <v>-1.0166</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3303</v>
+        <v>-0.138</v>
       </c>
       <c r="U17" t="n">
         <v>-0.8786</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.9841</v>
+        <v>-2.7243</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.5592</v>
+        <v>-3.04</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5752</v>
+        <v>0.3157</v>
       </c>
       <c r="G18" t="n">
         <v>-3.1982</v>
@@ -1858,13 +1858,13 @@
         <v>2.5656</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4822</v>
+        <v>-1.2225</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0521</v>
+        <v>-0.4287</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5343</v>
+        <v>-0.7938</v>
       </c>
       <c r="V18" t="n">
         <v>1.8796</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.4634</v>
+        <v>-2.8203</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.4376</v>
+        <v>-3.3029</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0258</v>
+        <v>0.4826</v>
       </c>
       <c r="G19" t="n">
         <v>-2.3824</v>
@@ -1936,13 +1936,13 @@
         <v>2.7489</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7432</v>
+        <v>-1.1001</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6192</v>
+        <v>-0.2462</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.3624</v>
+        <v>-0.8539</v>
       </c>
       <c r="V19" t="n">
         <v>1.5785</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.4465</v>
+        <v>-3.0721</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.0461</v>
+        <v>-3.8538</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5997</v>
+        <v>0.7817</v>
       </c>
       <c r="G20" t="n">
         <v>-2.9128</v>
@@ -2014,13 +2014,13 @@
         <v>2.9321</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3504</v>
+        <v>-0.976</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3325</v>
+        <v>-0.1402</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.0179</v>
+        <v>-0.8358</v>
       </c>
       <c r="V20" t="n">
         <v>0.6335</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.8026</v>
+        <v>-3.38</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.4925</v>
+        <v>-3.3964</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.31</v>
+        <v>0.0163</v>
       </c>
       <c r="G21" t="n">
         <v>-1.3035</v>
@@ -2092,13 +2092,13 @@
         <v>0.733</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0775</v>
+        <v>-0.655</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4955</v>
+        <v>-0.3993</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5821</v>
+        <v>-0.2557</v>
       </c>
       <c r="V21" t="n">
         <v>-0.3219</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.5656</v>
+        <v>-4.0513</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.2372</v>
+        <v>-3.4295</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3285</v>
+        <v>-0.6218</v>
       </c>
       <c r="G22" t="n">
         <v>-4.5956</v>
@@ -2170,13 +2170,13 @@
         <v>2.3823</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.4361</v>
+        <v>-0.9217</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2715</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.7076</v>
+        <v>-1.001</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.9326</v>
+        <v>-5.1868</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.5017</v>
+        <v>-5.0209</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.431</v>
+        <v>-0.1659</v>
       </c>
       <c r="G23" t="n">
         <v>-2.7743</v>
@@ -2248,13 +2248,13 @@
         <v>2.3823</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.8205</v>
+        <v>-2.0747</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.3401</v>
+        <v>-0.8593</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.4804</v>
+        <v>-1.2153</v>
       </c>
       <c r="V23" t="n">
         <v>0.945</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.578900000000001</v>
+        <v>-7.9349</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.4317</v>
+        <v>-6.1432</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.1472</v>
+        <v>-1.7917</v>
       </c>
       <c r="G24" t="n">
         <v>-4.7596</v>
@@ -2326,13 +2326,13 @@
         <v>2.0158</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.17</v>
+        <v>-1.526</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5701000000000001</v>
+        <v>-0.2816</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.5999</v>
+        <v>-1.2444</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-30.2921</v>
+        <v>-27.728</v>
       </c>
       <c r="E25" t="n">
         <v>-24.6831</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.6089</v>
+        <v>-3.045</v>
       </c>
       <c r="G25" t="n">
         <v>-20.2556</v>
@@ -2404,13 +2404,13 @@
         <v>17.4094</v>
       </c>
       <c r="S25" t="n">
-        <v>-12.9184</v>
+        <v>-10.3543</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.677</v>
+        <v>-2.6769</v>
       </c>
       <c r="U25" t="n">
-        <v>-10.2415</v>
+        <v>-7.6775</v>
       </c>
       <c r="V25" t="n">
         <v>4.7147</v>
